--- a/data/trans_bre/P16A06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,72</t>
+          <t>-0,79; 1,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,0</t>
+          <t>1,17; 4,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,93</t>
+          <t>3,8; 8,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,04</t>
+          <t>2,97; 7,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 256,08</t>
+          <t>-49,42; 273,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,03; 466,57</t>
+          <t>42,03; 459,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>104,7; 530,43</t>
+          <t>105,58; 511,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,8; 155,76</t>
+          <t>34,93; 141,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,13</t>
+          <t>0,25; 3,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,63</t>
+          <t>4,87; 8,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,98</t>
+          <t>1,39; 5,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,5</t>
+          <t>4,67; 8,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 282,87</t>
+          <t>7,4; 296,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>285,78; 1509,17</t>
+          <t>310,3; 1424,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,27; 301,24</t>
+          <t>39,83; 276,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>117,29; 537,3</t>
+          <t>118,18; 534,54</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,77</t>
+          <t>1,71; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,5</t>
+          <t>0,75; 5,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,81</t>
+          <t>2,36; 6,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,3</t>
+          <t>-2,47; 5,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,51; 498,6</t>
+          <t>57,41; 502,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 356,96</t>
+          <t>15,4; 387,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,88; 395,32</t>
+          <t>67,42; 414,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 129,89</t>
+          <t>-34,7; 138,04</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,69</t>
+          <t>0,88; 4,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,36</t>
+          <t>1,55; 5,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,17</t>
+          <t>3,7; 8,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,47</t>
+          <t>1,93; 7,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 201,36</t>
+          <t>18,52; 185,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,05; 270,71</t>
+          <t>34,55; 264,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,13; 350,6</t>
+          <t>90,75; 334,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 150,2</t>
+          <t>27,06; 146,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,07</t>
+          <t>1,37; 3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,29</t>
+          <t>3,17; 5,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,95</t>
+          <t>3,8; 6,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,54</t>
+          <t>2,96; 6,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,98; 192,36</t>
+          <t>57,82; 186,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>124,9; 305,31</t>
+          <t>124,49; 312,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>123,51; 268,22</t>
+          <t>120,81; 265,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,99; 158,24</t>
+          <t>60,65; 167,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,79</t>
+          <t>-0,83; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,96</t>
+          <t>1,33; 5,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,67</t>
+          <t>3,55; 8,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,8</t>
+          <t>2,93; 8,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 273,78</t>
+          <t>-48,85; 242,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,03; 459,5</t>
+          <t>43,93; 447,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>105,58; 511,64</t>
+          <t>102,32; 535,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,93; 141,36</t>
+          <t>32,94; 157,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>221,37%</t>
+          <t>143,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,05</t>
+          <t>0,23; 3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,71</t>
+          <t>4,94; 8,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,03</t>
+          <t>1,25; 4,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,92</t>
+          <t>3,7; 7,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 296,13</t>
+          <t>2,18; 291,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>310,3; 1424,7</t>
+          <t>293,95; 1450,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,83; 276,07</t>
+          <t>35,69; 291,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>118,18; 534,54</t>
+          <t>76,52; 247,58</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,55</t>
+          <t>1,49; 5,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,24</t>
+          <t>0,67; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,8</t>
+          <t>2,39; 6,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 5,47</t>
+          <t>1,86; 6,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,41; 502,76</t>
+          <t>43,01; 459,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 387,32</t>
+          <t>10,98; 316,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,42; 414,59</t>
+          <t>64,42; 438,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 138,04</t>
+          <t>27,8; 171,29</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,48</t>
+          <t>0,97; 4,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,69</t>
+          <t>1,52; 5,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,19</t>
+          <t>3,41; 8,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,23</t>
+          <t>3,57; 7,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 185,54</t>
+          <t>22,27; 202,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,55; 264,4</t>
+          <t>34,53; 247,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,75; 334,49</t>
+          <t>80,58; 339,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,06; 146,7</t>
+          <t>50,06; 161,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>102,84%</t>
+          <t>101,63%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,39; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,18</t>
+          <t>3,22; 5,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,04</t>
+          <t>3,83; 5,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,42</t>
+          <t>4,15; 6,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,82; 186,96</t>
+          <t>59,81; 182,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>124,49; 312,54</t>
+          <t>127,29; 316,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>120,81; 265,86</t>
+          <t>122,72; 266,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,65; 167,14</t>
+          <t>73,06; 139,2</t>
         </is>
       </c>
     </row>
